--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIII/LTAIPT_A63F23B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIII/LTAIPT_A63F23B.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E5FA3D-90B5-402F-B716-F3E30C720988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,30 +20,28 @@
     <sheet name="Hidden_4" sheetId="5" r:id="rId5"/>
     <sheet name="Hidden_5" sheetId="6" r:id="rId6"/>
     <sheet name="Hidden_6" sheetId="7" r:id="rId7"/>
-    <sheet name="Hidden_7" sheetId="8" r:id="rId8"/>
-    <sheet name="Tabla_436254" sheetId="9" r:id="rId9"/>
-    <sheet name="Hidden_1_Tabla_436254" sheetId="10" r:id="rId10"/>
-    <sheet name="Hidden_2_Tabla_436254" sheetId="11" r:id="rId11"/>
-    <sheet name="Tabla_436255" sheetId="12" r:id="rId12"/>
-    <sheet name="Tabla_436256" sheetId="13" r:id="rId13"/>
+    <sheet name="Tabla_436254" sheetId="8" r:id="rId8"/>
+    <sheet name="Hidden_1_Tabla_436254" sheetId="9" r:id="rId9"/>
+    <sheet name="Hidden_2_Tabla_436254" sheetId="10" r:id="rId10"/>
+    <sheet name="Tabla_436255" sheetId="11" r:id="rId11"/>
+    <sheet name="Tabla_436256" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="Hidden_1_Tabla_4362547">Hidden_1_Tabla_436254!$A$1:$A$2</definedName>
+    <definedName name="Hidden_1_Tabla_4362546">Hidden_1_Tabla_436254!$A$1:$A$2</definedName>
     <definedName name="Hidden_14">Hidden_1!$A$1:$A$3</definedName>
-    <definedName name="Hidden_2_Tabla_4362549">Hidden_2_Tabla_436254!$A$1:$A$3</definedName>
+    <definedName name="Hidden_2_Tabla_4362548">Hidden_2_Tabla_436254!$A$1:$A$3</definedName>
     <definedName name="Hidden_26">Hidden_2!$A$1:$A$4</definedName>
     <definedName name="Hidden_38">Hidden_3!$A$1:$A$10</definedName>
     <definedName name="Hidden_410">Hidden_4!$A$1:$A$2</definedName>
     <definedName name="Hidden_519">Hidden_5!$A$1:$A$4</definedName>
     <definedName name="Hidden_623">Hidden_6!$A$1:$A$3</definedName>
-    <definedName name="Hidden_724">Hidden_7!$A$1:$A$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="211">
   <si>
     <t>48975</t>
   </si>
@@ -147,9 +151,6 @@
     <t>436250</t>
   </si>
   <si>
-    <t>436261</t>
-  </si>
-  <si>
     <t>571931</t>
   </si>
   <si>
@@ -177,9 +178,6 @@
     <t>436263</t>
   </si>
   <si>
-    <t>436251</t>
-  </si>
-  <si>
     <t>436257</t>
   </si>
   <si>
@@ -255,9 +253,6 @@
     <t xml:space="preserve">Fecha de término de la campaña o aviso institucional </t>
   </si>
   <si>
-    <t>ESTE CRITERIO APLICA PARA EJERCICIOS ANTERIORES AL 01/04/2023 -&gt; Sexo (catálogo)</t>
-  </si>
-  <si>
     <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
   </si>
   <si>
@@ -273,7 +268,7 @@
     <t>Nivel socioeconómico</t>
   </si>
   <si>
-    <t>Respecto a los proveedores y su contratación 
+    <t>Respecto a la(s) persona(s) proveedora(s) y su contratación 
 Tabla_436254</t>
   </si>
   <si>
@@ -288,25 +283,13 @@
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
-    <t>Fecha de validación</t>
-  </si>
-  <si>
     <t>Fecha de actualización</t>
   </si>
   <si>
     <t>Nota</t>
   </si>
   <si>
-    <t>6A47C70320CBB688A7C4D4B3F895BA53</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
+    <t>2024</t>
   </si>
   <si>
     <t>Solicitante</t>
@@ -327,21 +310,12 @@
     <t>Aviso institucional</t>
   </si>
   <si>
-    <t>Arranca en el plantel 01 del cobat estrategia contra las adicciones</t>
-  </si>
-  <si>
-    <t>Arranca en el plantel 01 del cobat estrategia contra las adicciones.</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
     <t>Informativo</t>
   </si>
   <si>
-    <t>Boletin No. 20</t>
-  </si>
-  <si>
     <t>Departamento de Información y Relaciones Públicas.</t>
   </si>
   <si>
@@ -351,13 +325,7 @@
     <t>Local</t>
   </si>
   <si>
-    <t>17/04/2023</t>
-  </si>
-  <si>
-    <t>18/04/2023</t>
-  </si>
-  <si>
-    <t>Femenino y masculino</t>
+    <t>Mujeres y Hombres</t>
   </si>
   <si>
     <t>Tlaxcala</t>
@@ -369,79 +337,91 @@
     <t>15 años en adelante</t>
   </si>
   <si>
-    <t>6579257</t>
-  </si>
-  <si>
-    <t>19/04/2023</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 1 de abril de 2023 al 30 de junio de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no celebra ningun tipo de erogacion de recursos por contratacion de servicios de impresion, difusion y publicidad.</t>
-  </si>
-  <si>
-    <t>544A0218FB689028AD6632A9780C6C7C</t>
-  </si>
-  <si>
-    <t>Club de montañismo del cobat conquista la cima de el cuatlapanga</t>
-  </si>
-  <si>
-    <t>Boletin No. 24</t>
-  </si>
-  <si>
-    <t>30/04/2023</t>
-  </si>
-  <si>
-    <t>6579261</t>
-  </si>
-  <si>
-    <t>7CA6A0DE33B8B7E72000A4D0B2176677</t>
-  </si>
-  <si>
-    <t>Cobat celebra el 40 aniversario del plantel 08 ixtacuixtla</t>
-  </si>
-  <si>
-    <t>Boletin No. 23</t>
-  </si>
-  <si>
-    <t>25/04/2023</t>
-  </si>
-  <si>
-    <t>26/04/2023</t>
-  </si>
-  <si>
-    <t>6579260</t>
-  </si>
-  <si>
-    <t>087E4C4C68C1F7B1CD7D0242EBA3963F</t>
-  </si>
-  <si>
-    <t>Estudiantes del COBAT demuestran su habilidad oral en el concurso  de declamación y cuenta cuentos</t>
-  </si>
-  <si>
-    <t>Boletin No. 22</t>
-  </si>
-  <si>
-    <t>24/04/2023</t>
-  </si>
-  <si>
-    <t>6579259</t>
-  </si>
-  <si>
-    <t>37ADB6C1AECC077DF6B0C321036602D2</t>
-  </si>
-  <si>
-    <t>Cobat inaugura xxxviii juegos deportivos Interbachilleres 2023</t>
-  </si>
-  <si>
-    <t>Boletin No. 21</t>
-  </si>
-  <si>
-    <t>20/04/2023</t>
-  </si>
-  <si>
-    <t>21/04/2023</t>
-  </si>
-  <si>
-    <t>6579258</t>
+    <t>855562DF4E7070CC80339D2ACE566E89</t>
+  </si>
+  <si>
+    <t>01/04/2024</t>
+  </si>
+  <si>
+    <t>30/06/2024</t>
+  </si>
+  <si>
+    <t>Trascendencia en equipo de cómputo del cobat tras década de rezago</t>
+  </si>
+  <si>
+    <t>Boletin No. 8</t>
+  </si>
+  <si>
+    <t>27/06/2024</t>
+  </si>
+  <si>
+    <t>14416257</t>
+  </si>
+  <si>
+    <t>02/07/2024</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 1 de abril de 2024 al 30 de junio de 2024, el Colegio de Bachilleres del Estado de Tlaxcala no celebra ningun tipo de erogacion de recursos por contratacion de servicios de impresion, difusion y publicidad.</t>
+  </si>
+  <si>
+    <t>D95763713573E1EA6765F7678D518BBA</t>
+  </si>
+  <si>
+    <t>El crit realiza estudios de espirometría al personal administrativo del cobat</t>
+  </si>
+  <si>
+    <t>Boletin No. 5</t>
+  </si>
+  <si>
+    <t>25/04/2024</t>
+  </si>
+  <si>
+    <t>14416254</t>
+  </si>
+  <si>
+    <t>CDA3A6FBBB25906BBB90F196E16BAEC3</t>
+  </si>
+  <si>
+    <t>Cobat y la coordinación de bienestar animal firman convenio de colaboración</t>
+  </si>
+  <si>
+    <t>Boletin No. 4</t>
+  </si>
+  <si>
+    <t>15/04/2024</t>
+  </si>
+  <si>
+    <t>14416253</t>
+  </si>
+  <si>
+    <t>EB07B934E0737215FC8A2FEB98D94219</t>
+  </si>
+  <si>
+    <t>Encabeza gobernadora entrega de equipo de cómputo y mobiliario a planteles del cobat</t>
+  </si>
+  <si>
+    <t>Boletin No. 7</t>
+  </si>
+  <si>
+    <t>25/06/2024</t>
+  </si>
+  <si>
+    <t>14416256</t>
+  </si>
+  <si>
+    <t>E574039468CA491AA50B71F9DF165F4C</t>
+  </si>
+  <si>
+    <t>Realiza plantel 06 contla del cobat eco rally deportivo y social</t>
+  </si>
+  <si>
+    <t>Boletin No. 6</t>
+  </si>
+  <si>
+    <t>03/05/2024</t>
+  </si>
+  <si>
+    <t>14416255</t>
   </si>
   <si>
     <t>Contratante</t>
@@ -498,21 +478,12 @@
     <t>Delegacional o municipal</t>
   </si>
   <si>
-    <t>Femenino</t>
-  </si>
-  <si>
-    <t>Masculino</t>
-  </si>
-  <si>
     <t>Mujer</t>
   </si>
   <si>
     <t>Hombre</t>
   </si>
   <si>
-    <t>Mujeres y Hombres</t>
-  </si>
-  <si>
     <t>56431</t>
   </si>
   <si>
@@ -525,9 +496,6 @@
     <t>56434</t>
   </si>
   <si>
-    <t>56439</t>
-  </si>
-  <si>
     <t>77787</t>
   </si>
   <si>
@@ -549,16 +517,13 @@
     <t>Razón social</t>
   </si>
   <si>
-    <t>Nombre(s) de la/s persona/s proveedora/s y/o responsable/s de publicar la campaña o la comunicación</t>
-  </si>
-  <si>
-    <t>Primer apellido de la/s persona/s proveedora/s y/o responsable/s de publicar la campaña o la comunicación</t>
-  </si>
-  <si>
-    <t>Segundo apellido de la/s persona/s proveedora/s y/o responsable/s de publicar la campaña o la comunicación</t>
-  </si>
-  <si>
-    <t>Nombre(s) de los proveedores y/o responsables</t>
+    <t>Nombre completo de la(s) persona(s) proveedora(s) y/o responsable(s) de publicar la campaña o la comunicación</t>
+  </si>
+  <si>
+    <t>Primer apellido de la(s) persona(s) proveedora(s) y/o responsable(s) de publicar la campaña o la comunicación</t>
+  </si>
+  <si>
+    <t>Segundo apellido de la(s) persona(s) proveedora(s) y/o responsable(s) de publicar la campaña o la comunicación</t>
   </si>
   <si>
     <t>Sexo (catálogo)</t>
@@ -567,13 +532,13 @@
     <t>Registro Federal de Contribuyente</t>
   </si>
   <si>
-    <t>Procedimiento de contratación</t>
+    <t>Procedimiento de contratación (catálogo)</t>
   </si>
   <si>
     <t>Fundamento jurídico del proceso de contratación</t>
   </si>
   <si>
-    <t>Descripción breve de las razones que justifican la elección del/la proveedor/a</t>
+    <t>Descripción breve de las razones que justifican la elección de la persona proveedora</t>
   </si>
   <si>
     <t>Licitación pública</t>
@@ -717,7 +682,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -816,6 +781,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -831,44 +799,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -896,14 +864,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -931,6 +916,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -942,175 +944,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AJ12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -1121,9 +1099,9 @@
     <col min="9" max="9" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="88.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="81.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="88.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="74.85546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="56.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="15.140625" bestFit="1" customWidth="1"/>
@@ -1133,27 +1111,25 @@
     <col min="21" max="21" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="44" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="46.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="75" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="181.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="18" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="30" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="20" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="193.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="30" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="20" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="196.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1170,7 +1146,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -1185,7 +1161,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -1256,7 +1232,7 @@
         <v>8</v>
       </c>
       <c r="Y4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z4" t="s">
         <v>6</v>
@@ -1268,7 +1244,7 @@
         <v>6</v>
       </c>
       <c r="AC4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="s">
         <v>11</v>
@@ -1277,22 +1253,16 @@
         <v>11</v>
       </c>
       <c r="AF4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>12</v>
-      </c>
-      <c r="AJ4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -1392,16 +1362,10 @@
       <c r="AH5" t="s">
         <v>46</v>
       </c>
-      <c r="AI5" t="s">
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1436,669 +1400,631 @@
       <c r="AF6" s="5"/>
       <c r="AG6" s="5"/>
       <c r="AH6" s="5"/>
-      <c r="AI6" s="5"/>
-      <c r="AJ6" s="5"/>
-    </row>
-    <row r="7" spans="1:36" ht="39" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:34" ht="39" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="AA7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="AB7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AD7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AE7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="AD7" s="2" t="s">
+      <c r="AF7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AG7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AF7" s="2" t="s">
+      <c r="AH7" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="AG7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AH7" s="2" t="s">
+      <c r="C8" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="AJ7" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="8" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="K8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y8" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="Z8" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="AA8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH8" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD8" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AE8" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AF8" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AG8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH8" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AI8" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AJ8" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>6</v>
       </c>
       <c r="K9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y9" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="M9" s="3" t="s">
+      <c r="Z9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AB9" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD9" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE9" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AF9" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG9" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH9" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AI9" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AJ9" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>6</v>
       </c>
       <c r="K10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y10" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="M10" s="3" t="s">
+      <c r="Z10" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="X10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y10" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z10" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AB10" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC10" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD10" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE10" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF10" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH10" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AI10" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AJ10" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>6</v>
       </c>
       <c r="K11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="M11" s="3" t="s">
+      <c r="Z11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG11" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH11" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="V11" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y11" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z11" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA11" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AB11" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC11" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD11" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="AE11" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="AF11" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="AG11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH11" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AI11" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AJ11" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>6</v>
       </c>
       <c r="K12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y12" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="X12" s="3" t="s">
+      <c r="Z12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH12" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC12" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD12" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE12" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AF12" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AG12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH12" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AI12" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AJ12" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AJ6"/>
+    <mergeCell ref="A6:AH6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -2106,27 +2032,24 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E155">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E188" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G155">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G188" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>Hidden_26</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I155">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I188" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>Hidden_38</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K155">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K188" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>Hidden_410</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T8:T155">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T8:T188" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>Hidden_519</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X155">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X188" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>Hidden_623</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y8:Y155">
-      <formula1>Hidden_724</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2134,18 +2057,23 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>154</v>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2154,32 +2082,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2229,70 +2132,70 @@
     </row>
     <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D2" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E2" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="F2" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="G2" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="H2" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="I2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="J2" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="K2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="L2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2300,8 +2203,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2329,10 +2232,10 @@
         <v>9</v>
       </c>
       <c r="F1" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="G1" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="H1" t="s">
         <v>10</v>
@@ -2350,81 +2253,81 @@
         <v>6</v>
       </c>
       <c r="M1" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="E2" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="F2" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="G2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="H2" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="I2" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="J2" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="K2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="L2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="M2" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -2433,23 +2336,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -2458,28 +2361,28 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2488,58 +2391,58 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2548,18 +2451,18 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2568,28 +2471,28 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2598,23 +2501,23 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2623,156 +2526,141 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="118.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="116.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="118.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="88.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>156</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>164</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G4:G201" xr:uid="{00000000-0002-0000-0700-000000000000}">
+      <formula1>Hidden_1_Tabla_4362546</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I201" xr:uid="{00000000-0002-0000-0700-000001000000}">
+      <formula1>Hidden_2_Tabla_4362548</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="107.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="112.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="114.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="52.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="81.140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J2" t="s">
-        <v>164</v>
-      </c>
-      <c r="K2" t="s">
-        <v>165</v>
-      </c>
-      <c r="L2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>177</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H201">
-      <formula1>Hidden_1_Tabla_4362547</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J4:J201">
-      <formula1>Hidden_2_Tabla_4362549</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIII/LTAIPT_A63F23B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIII/LTAIPT_A63F23B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E5FA3D-90B5-402F-B716-F3E30C720988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD06F4B9-284D-4DE6-A0CD-8CB710418452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="234">
   <si>
     <t>48975</t>
   </si>
@@ -289,9 +289,18 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>56686895A35727C58857EDF08853CDFC</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t>Solicitante</t>
   </si>
   <si>
@@ -310,12 +319,18 @@
     <t>Aviso institucional</t>
   </si>
   <si>
+    <t>Presenta Cobat el Libro Papalotla, tierra de hombres valientes</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
     <t>Informativo</t>
   </si>
   <si>
+    <t>Boletin No. 15</t>
+  </si>
+  <si>
     <t>Departamento de Información y Relaciones Públicas.</t>
   </si>
   <si>
@@ -325,6 +340,9 @@
     <t>Local</t>
   </si>
   <si>
+    <t>13/09/2024</t>
+  </si>
+  <si>
     <t>Mujeres y Hombres</t>
   </si>
   <si>
@@ -334,94 +352,145 @@
     <t>Preparatoria</t>
   </si>
   <si>
+    <t>17 años en adelante</t>
+  </si>
+  <si>
+    <t>15970768</t>
+  </si>
+  <si>
+    <t>03/10/2024</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 1 de julio de 2024 al 30 de septiembre de 2024, el Colegio de Bachilleres del Estado de Tlaxcala no celebra ningun tipo de erogacion de recursos por contratacion de servicios de impresion, difusion y publicidad.</t>
+  </si>
+  <si>
+    <t>15BA8C13182ED78D2E8AE1321D11B729</t>
+  </si>
+  <si>
+    <t>Modernización del equipamiento del Cobat permite abatir años de regazo</t>
+  </si>
+  <si>
+    <t>Boletin No. 14</t>
+  </si>
+  <si>
+    <t>22/08/2024</t>
+  </si>
+  <si>
+    <t>16 años en adelante</t>
+  </si>
+  <si>
+    <t>15970767</t>
+  </si>
+  <si>
+    <t>52F504BE30BACD2ED31A5270786CA4FF</t>
+  </si>
+  <si>
+    <t>Cobat refuerza la seguridad en cooperación con SSC</t>
+  </si>
+  <si>
+    <t>Boletin No. 13</t>
+  </si>
+  <si>
+    <t>05/08/2024</t>
+  </si>
+  <si>
     <t>15 años en adelante</t>
   </si>
   <si>
-    <t>855562DF4E7070CC80339D2ACE566E89</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
-    <t>Trascendencia en equipo de cómputo del cobat tras década de rezago</t>
-  </si>
-  <si>
-    <t>Boletin No. 8</t>
-  </si>
-  <si>
-    <t>27/06/2024</t>
-  </si>
-  <si>
-    <t>14416257</t>
-  </si>
-  <si>
-    <t>02/07/2024</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 1 de abril de 2024 al 30 de junio de 2024, el Colegio de Bachilleres del Estado de Tlaxcala no celebra ningun tipo de erogacion de recursos por contratacion de servicios de impresion, difusion y publicidad.</t>
-  </si>
-  <si>
-    <t>D95763713573E1EA6765F7678D518BBA</t>
-  </si>
-  <si>
-    <t>El crit realiza estudios de espirometría al personal administrativo del cobat</t>
-  </si>
-  <si>
-    <t>Boletin No. 5</t>
-  </si>
-  <si>
-    <t>25/04/2024</t>
-  </si>
-  <si>
-    <t>14416254</t>
-  </si>
-  <si>
-    <t>CDA3A6FBBB25906BBB90F196E16BAEC3</t>
-  </si>
-  <si>
-    <t>Cobat y la coordinación de bienestar animal firman convenio de colaboración</t>
-  </si>
-  <si>
-    <t>Boletin No. 4</t>
-  </si>
-  <si>
-    <t>15/04/2024</t>
-  </si>
-  <si>
-    <t>14416253</t>
-  </si>
-  <si>
-    <t>EB07B934E0737215FC8A2FEB98D94219</t>
-  </si>
-  <si>
-    <t>Encabeza gobernadora entrega de equipo de cómputo y mobiliario a planteles del cobat</t>
-  </si>
-  <si>
-    <t>Boletin No. 7</t>
-  </si>
-  <si>
-    <t>25/06/2024</t>
-  </si>
-  <si>
-    <t>14416256</t>
-  </si>
-  <si>
-    <t>E574039468CA491AA50B71F9DF165F4C</t>
-  </si>
-  <si>
-    <t>Realiza plantel 06 contla del cobat eco rally deportivo y social</t>
-  </si>
-  <si>
-    <t>Boletin No. 6</t>
-  </si>
-  <si>
-    <t>03/05/2024</t>
-  </si>
-  <si>
-    <t>14416255</t>
+    <t>15970766</t>
+  </si>
+  <si>
+    <t>24F8FA751642556D5A9CF17E4ABE231B</t>
+  </si>
+  <si>
+    <t>Firma Convenio el subsistema con el ITIFE, en el marco del Programa FAM 2024</t>
+  </si>
+  <si>
+    <t>Boletin No. 12</t>
+  </si>
+  <si>
+    <t>02/08/2024</t>
+  </si>
+  <si>
+    <t>15970765</t>
+  </si>
+  <si>
+    <t>EE00A266D08CC47FE82BD69C2D9401CE</t>
+  </si>
+  <si>
+    <t>Finaliza Primer programa COBAT - TECNOLOCHICAS</t>
+  </si>
+  <si>
+    <t>Boletin No. 10</t>
+  </si>
+  <si>
+    <t>10/07/2024</t>
+  </si>
+  <si>
+    <t>15970763</t>
+  </si>
+  <si>
+    <t>716D3B3A1E7E9488F92F318029A1D284</t>
+  </si>
+  <si>
+    <t>El cobat 19 Xaloztoc gana el Concurso de Banda de Guerra Interbachilleres 2024</t>
+  </si>
+  <si>
+    <t>Boletin No. 11</t>
+  </si>
+  <si>
+    <t>12/07/2024</t>
+  </si>
+  <si>
+    <t>15970764</t>
+  </si>
+  <si>
+    <t>B4C78E4FDF4B3BD4552AA4F98A534513</t>
+  </si>
+  <si>
+    <t>Cobat realiza sinergia con autoridades municipales electas</t>
+  </si>
+  <si>
+    <t>Boletin No. 9</t>
+  </si>
+  <si>
+    <t>04/07/2024</t>
+  </si>
+  <si>
+    <t>15970762</t>
+  </si>
+  <si>
+    <t>2B211273F10BC0DFF7E1840CC05BDB3A</t>
+  </si>
+  <si>
+    <t>Realiza Cobat Magna Conferencia Cero Tolerancia a la Inseguridad y a las Adicciones</t>
+  </si>
+  <si>
+    <t>Boletin No. 17</t>
+  </si>
+  <si>
+    <t>19 años en adelante</t>
+  </si>
+  <si>
+    <t>15970770</t>
+  </si>
+  <si>
+    <t>CD9D0C1195EB995EF44EF6E757A10D26</t>
+  </si>
+  <si>
+    <t>Cobat Realiza XXXIX Certamen Estatal de Oratoria Xicohtencatl Axayacatzin</t>
+  </si>
+  <si>
+    <t>Boletin No. 16</t>
+  </si>
+  <si>
+    <t>26/09/2024</t>
+  </si>
+  <si>
+    <t>18 años en adelante</t>
+  </si>
+  <si>
+    <t>15970769</t>
   </si>
   <si>
     <t>Contratante</t>
@@ -1085,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH12"/>
+  <dimension ref="A1:AH16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
@@ -1504,88 +1573,88 @@
     </row>
     <row r="8" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y8" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="R8" s="3" t="s">
+      <c r="Z8" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="U8" s="3" t="s">
+      <c r="AA8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB8" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>103</v>
@@ -1597,7 +1666,7 @@
         <v>103</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AG8" s="3" t="s">
         <v>104</v>
@@ -1611,64 +1680,64 @@
         <v>106</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>6</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>107</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>107</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>108</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>109</v>
@@ -1677,31 +1746,31 @@
         <v>109</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="Z9" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AC9" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE9" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AG9" s="3" t="s">
         <v>104</v>
@@ -1712,100 +1781,100 @@
     </row>
     <row r="10" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>6</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="U10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="X10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y10" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z10" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB10" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="AC10" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AD10" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AE10" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AF10" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AG10" s="3" t="s">
         <v>104</v>
@@ -1816,100 +1885,100 @@
     </row>
     <row r="11" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>6</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="U11" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB11" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="V11" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y11" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z11" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB11" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="AC11" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AD11" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AE11" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AF11" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AG11" s="3" t="s">
         <v>104</v>
@@ -1920,105 +1989,521 @@
     </row>
     <row r="12" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>6</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="U12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB12" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="AC12" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD12" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE12" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AF12" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AG12" s="3" t="s">
         <v>104</v>
       </c>
       <c r="AH12" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="W13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="X13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AE13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AF13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH13" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA15" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="AD15" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG15" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH15" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="X16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z16" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA16" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC16" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD16" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AE16" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AF16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG16" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH16" s="3" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2033,22 +2518,22 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E188" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E191" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G188" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G191" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>Hidden_26</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I188" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I191" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>Hidden_38</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K188" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K191" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>Hidden_410</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T8:T188" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T8:T191" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>Hidden_519</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X188" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X191" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>Hidden_623</formula1>
     </dataValidation>
   </dataValidations>
@@ -2063,17 +2548,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2132,70 +2617,70 @@
     </row>
     <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="D2" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="E2" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="F2" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="G2" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="H2" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="I2" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="J2" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="K2" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="L2" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -2232,10 +2717,10 @@
         <v>9</v>
       </c>
       <c r="F1" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="G1" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="H1" t="s">
         <v>10</v>
@@ -2253,81 +2738,81 @@
         <v>6</v>
       </c>
       <c r="M1" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="D2" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="E2" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="F2" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="G2" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="H2" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="I2" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="J2" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="K2" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="L2" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="M2" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -2342,17 +2827,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2367,22 +2852,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2397,52 +2882,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2457,12 +2942,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2477,22 +2962,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2507,17 +2992,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2572,64 +3057,64 @@
     </row>
     <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="E2" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="F2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="G2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="H2" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="I2" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="J2" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="K2" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2652,12 +3137,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
